--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>80.17742339603528</v>
+        <v>13.02883130185573</v>
       </c>
       <c r="D2" t="n">
-        <v>30.40596907642125</v>
+        <v>4.940969974918454</v>
       </c>
       <c r="E2" t="n">
-        <v>12.16130406273328</v>
+        <v>1.976211910194158</v>
       </c>
       <c r="F2" t="n">
-        <v>11.72919785066862</v>
+        <v>1.90599465073365</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>55.85481527056871</v>
+        <v>9.076407481467417</v>
       </c>
       <c r="D3" t="n">
-        <v>53.86436477775849</v>
+        <v>8.752959276385754</v>
       </c>
       <c r="E3" t="n">
-        <v>12.16130406273328</v>
+        <v>1.976211910194158</v>
       </c>
       <c r="F3" t="n">
-        <v>11.72919785066862</v>
+        <v>1.90599465073365</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
